--- a/03_Test_Scenario/TestScenario_Login.xlsx
+++ b/03_Test_Scenario/TestScenario_Login.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Manual-Tester-Portfolio\03_Test_Scenario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFED829E-31F8-4EDE-8108-242C89488E31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBFDF7C-BA40-45AF-BDBF-A3E0D5E40D5D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4116" yWindow="1248" windowWidth="17280" windowHeight="8964" xr2:uid="{8F7A0EB9-5408-478B-92A5-4C62A1CFF411}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F7A0EB9-5408-478B-92A5-4C62A1CFF411}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login Scenario" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,9 +33,164 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
+  <si>
+    <t>Scenario ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_001</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Login thành công với Email và Password hợp lệ</t>
+  </si>
+  <si>
+    <t>BR11, BR12</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_002</t>
+  </si>
+  <si>
+    <t>Để trống Email</t>
+  </si>
+  <si>
+    <t>BR01</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_003</t>
+  </si>
+  <si>
+    <t>Để trống Password</t>
+  </si>
+  <si>
+    <t>BR02</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_004</t>
+  </si>
+  <si>
+    <t>Email sai định dạng</t>
+  </si>
+  <si>
+    <t>BR03</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_005</t>
+  </si>
+  <si>
+    <t>Password nhỏ hơn 8 ký tự</t>
+  </si>
+  <si>
+    <t>BR04</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_006</t>
+  </si>
+  <si>
+    <t>Password lớn hơn 20 ký tự</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_007</t>
+  </si>
+  <si>
+    <t>Password sai</t>
+  </si>
+  <si>
+    <t>BR06</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_008</t>
+  </si>
+  <si>
+    <t>Sai Password quá 5 lần, tài khoản bị khóa</t>
+  </si>
+  <si>
+    <t>BR07</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_009</t>
+  </si>
+  <si>
+    <t>Hiển thị Password khi chọn Show Password</t>
+  </si>
+  <si>
+    <t>BR08</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_010</t>
+  </si>
+  <si>
+    <t>Ẩn Password khi bỏ chọn Show Password</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_011</t>
+  </si>
+  <si>
+    <t>Login với Remember Me được chọn</t>
+  </si>
+  <si>
+    <t>BR09</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_012</t>
+  </si>
+  <si>
+    <t>Login không chọn Remember Me</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_013</t>
+  </si>
+  <si>
+    <t>Chọn Forgot Password</t>
+  </si>
+  <si>
+    <t>BR10</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_014</t>
+  </si>
+  <si>
+    <t>Password phân biệt chữ hoa và chữ thường</t>
+  </si>
+  <si>
+    <t>BR05</t>
+  </si>
+  <si>
+    <t>SC_LOGIN_015</t>
+  </si>
+  <si>
+    <t>Dashboard hiển thị đúng tên sinh viên sau khi Login</t>
+  </si>
+  <si>
+    <t>BR12</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -43,16 +198,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +229,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7D7D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7D7D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7D7D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7D7D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7D7D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF7D7D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -380,9 +649,305 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A1E97A-05AA-4A13-A2E5-86183C2B7F67}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="50.88671875" customWidth="1"/>
+    <col min="4" max="4" width="27.109375" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E2:E16">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E16" xr:uid="{335705A3-99EE-4CD4-AB69-D55C91FB5FB1}">
+      <formula1>"High, Medium, Low"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/03_Test_Scenario/TestScenario_Login.xlsx
+++ b/03_Test_Scenario/TestScenario_Login.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Manual-Tester-Portfolio\03_Test_Scenario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBFDF7C-BA40-45AF-BDBF-A3E0D5E40D5D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B25B86-77E6-4C6E-B7AE-BA6740EEEAD7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F7A0EB9-5408-478B-92A5-4C62A1CFF411}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -162,12 +162,6 @@
     <t>SC_LOGIN_013</t>
   </si>
   <si>
-    <t>Chọn Forgot Password</t>
-  </si>
-  <si>
-    <t>BR10</t>
-  </si>
-  <si>
     <t>SC_LOGIN_014</t>
   </si>
   <si>
@@ -175,9 +169,6 @@
   </si>
   <si>
     <t>BR05</t>
-  </si>
-  <si>
-    <t>SC_LOGIN_015</t>
   </si>
   <si>
     <t>Dashboard hiển thị đúng tên sinh viên sau khi Login</t>
@@ -263,42 +254,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7D7D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -316,21 +272,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF7D7D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7D7D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7D7D"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -649,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A1E97A-05AA-4A13-A2E5-86183C2B7F67}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -888,18 +830,18 @@
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>8</v>
@@ -914,37 +856,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E16">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E2)))</formula>
+  <conditionalFormatting sqref="E2:E15">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E2)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E16" xr:uid="{335705A3-99EE-4CD4-AB69-D55C91FB5FB1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E15" xr:uid="{335705A3-99EE-4CD4-AB69-D55C91FB5FB1}">
       <formula1>"High, Medium, Low"</formula1>
     </dataValidation>
   </dataValidations>
